--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2021_T2_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2021_T2_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>73</t>
+    <t>67</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>1.358</t>
-  </si>
-  <si>
-    <t>(0.347)</t>
-  </si>
-  <si>
-    <t>6.452</t>
-  </si>
-  <si>
-    <t>(0.820)</t>
-  </si>
-  <si>
-    <t>2.850</t>
-  </si>
-  <si>
-    <t>(0.620)</t>
-  </si>
-  <si>
-    <t>22.881</t>
-  </si>
-  <si>
-    <t>(9.826)</t>
-  </si>
-  <si>
-    <t>6.423</t>
-  </si>
-  <si>
-    <t>(4.874)</t>
-  </si>
-  <si>
-    <t>10.534</t>
-  </si>
-  <si>
-    <t>(1.264)</t>
-  </si>
-  <si>
-    <t>6.586</t>
-  </si>
-  <si>
-    <t>(1.773)</t>
-  </si>
-  <si>
-    <t>5.665</t>
-  </si>
-  <si>
-    <t>(4.886)</t>
-  </si>
-  <si>
-    <t>32.900</t>
-  </si>
-  <si>
-    <t>(20.998)</t>
-  </si>
-  <si>
-    <t>14.232</t>
-  </si>
-  <si>
-    <t>(3.657)</t>
+    <t>1.114</t>
+  </si>
+  <si>
+    <t>(0.174)</t>
+  </si>
+  <si>
+    <t>6.970</t>
+  </si>
+  <si>
+    <t>(0.865)</t>
+  </si>
+  <si>
+    <t>2.740</t>
+  </si>
+  <si>
+    <t>(0.594)</t>
+  </si>
+  <si>
+    <t>10.033</t>
+  </si>
+  <si>
+    <t>(1.530)</t>
+  </si>
+  <si>
+    <t>1.668</t>
+  </si>
+  <si>
+    <t>(0.190)</t>
+  </si>
+  <si>
+    <t>11.463</t>
+  </si>
+  <si>
+    <t>(1.319)</t>
+  </si>
+  <si>
+    <t>3.876</t>
+  </si>
+  <si>
+    <t>(1.088)</t>
+  </si>
+  <si>
+    <t>0.636</t>
+  </si>
+  <si>
+    <t>(0.150)</t>
+  </si>
+  <si>
+    <t>11.176</t>
+  </si>
+  <si>
+    <t>(1.527)</t>
+  </si>
+  <si>
+    <t>9.085</t>
+  </si>
+  <si>
+    <t>(2.264)</t>
   </si>
   <si>
     <t>43</t>
@@ -198,7 +198,7 @@
     <t>(2.416)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>3.246**</t>
-  </si>
-  <si>
-    <t>1.563</t>
-  </si>
-  <si>
-    <t>-11.122</t>
-  </si>
-  <si>
-    <t>-4.781</t>
-  </si>
-  <si>
-    <t>0.140</t>
-  </si>
-  <si>
-    <t>-2.954</t>
-  </si>
-  <si>
-    <t>-5.035</t>
-  </si>
-  <si>
-    <t>-19.330</t>
-  </si>
-  <si>
-    <t>-3.817</t>
+    <t>0.330</t>
+  </si>
+  <si>
+    <t>2.728*</t>
+  </si>
+  <si>
+    <t>1.673*</t>
+  </si>
+  <si>
+    <t>1.726</t>
+  </si>
+  <si>
+    <t>-0.025</t>
+  </si>
+  <si>
+    <t>-0.788</t>
+  </si>
+  <si>
+    <t>-0.244</t>
+  </si>
+  <si>
+    <t>-0.007</t>
+  </si>
+  <si>
+    <t>2.395</t>
+  </si>
+  <si>
+    <t>1.330</t>
   </si>
 </sst>
 </file>
